--- a/docs/ai-case-import/AI自然语言用例导入模板.xlsx
+++ b/docs/ai-case-import/AI自然语言用例导入模板.xlsx
@@ -6,15 +6,14 @@
   <sheets>
     <sheet sheetId="1" name="用例清单" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="步骤明细" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="测试数据" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="填写说明" state="visible" r:id="rId7"/>
+    <sheet sheetId="3" name="填写说明" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="56">
   <si>
     <t>用例编号</t>
   </si>
@@ -64,151 +63,124 @@
     <t>用户列表只显示符合查询条件的用户</t>
   </si>
   <si>
-    <t>查询条件来自测试数据</t>
+    <t>查询条件直接填写在步骤明细的输入/期望值中</t>
   </si>
   <si>
     <t>步骤序号</t>
   </si>
   <si>
-    <t>操作描述</t>
-  </si>
-  <si>
-    <t>目标对象</t>
-  </si>
-  <si>
-    <t>数据引用</t>
-  </si>
-  <si>
-    <t>点击新增按钮，打开新增用户弹窗</t>
-  </si>
-  <si>
-    <t>新增按钮</t>
+    <t>动作类型</t>
+  </si>
+  <si>
+    <t>目标类型</t>
+  </si>
+  <si>
+    <t>目标名称</t>
+  </si>
+  <si>
+    <t>输入/期望值</t>
+  </si>
+  <si>
+    <t>匹配方式</t>
+  </si>
+  <si>
+    <t>点击(click)</t>
+  </si>
+  <si>
+    <t>按钮(button)</t>
+  </si>
+  <si>
+    <t>新增</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>点击后打开弹窗需要写清楚</t>
-  </si>
-  <si>
-    <t>输入用户名称</t>
-  </si>
-  <si>
-    <t>用户名称输入框</t>
-  </si>
-  <si>
-    <t>username</t>
-  </si>
-  <si>
-    <t>数据引用与测试数据中的数据标识一致</t>
-  </si>
-  <si>
-    <t>输入手机号</t>
-  </si>
-  <si>
-    <t>手机号输入框</t>
-  </si>
-  <si>
-    <t>phone</t>
-  </si>
-  <si>
-    <t>点击保存按钮</t>
-  </si>
-  <si>
-    <t>保存按钮</t>
-  </si>
-  <si>
-    <t>输入用户名称查询条件</t>
-  </si>
-  <si>
-    <t>用户名称查询框</t>
-  </si>
-  <si>
-    <t>searchName</t>
-  </si>
-  <si>
-    <t>点击查询按钮</t>
-  </si>
-  <si>
-    <t>查询按钮</t>
-  </si>
-  <si>
-    <t>数据标识</t>
-  </si>
-  <si>
-    <t>数据名称</t>
-  </si>
-  <si>
-    <t>数据值</t>
+    <t>打开新增用户弹窗</t>
+  </si>
+  <si>
+    <t>填写(fill)</t>
+  </si>
+  <si>
+    <t>输入框(input)</t>
+  </si>
+  <si>
+    <t>用户名称</t>
+  </si>
+  <si>
+    <t>测试用户001</t>
+  </si>
+  <si>
+    <t>选择(select)</t>
+  </si>
+  <si>
+    <t>下拉框(select)</t>
+  </si>
+  <si>
+    <t>用户状态</t>
+  </si>
+  <si>
+    <t>启用</t>
+  </si>
+  <si>
+    <t>保存</t>
+  </si>
+  <si>
+    <t>用户名称查询条件</t>
+  </si>
+  <si>
+    <t>检查可见(assertVisible)</t>
+  </si>
+  <si>
+    <t>表格(table)</t>
+  </si>
+  <si>
+    <t>用户列表</t>
+  </si>
+  <si>
+    <t>检查查询结果可见</t>
+  </si>
+  <si>
+    <t>项目</t>
   </si>
   <si>
     <t>说明</t>
   </si>
   <si>
-    <t>用户名称</t>
-  </si>
-  <si>
-    <t>测试用户001</t>
-  </si>
-  <si>
-    <t>用于新增用户名称，并用于后续列表查看</t>
-  </si>
-  <si>
-    <t>手机号</t>
-  </si>
-  <si>
-    <t>13800000001</t>
-  </si>
-  <si>
-    <t>用于新增用户手机号</t>
-  </si>
-  <si>
-    <t>查询用户名称</t>
-  </si>
-  <si>
-    <t>用于查询用户列表</t>
-  </si>
-  <si>
-    <t>项目</t>
-  </si>
-  <si>
-    <t>模板用途</t>
-  </si>
-  <si>
-    <t>用于批量填写自然语言测试用例，上传后生成可编辑草稿。</t>
-  </si>
-  <si>
-    <t>工作表范围</t>
-  </si>
-  <si>
-    <t>工作簿只包含用例清单、步骤明细、测试数据、填写说明四个工作表。</t>
-  </si>
-  <si>
-    <t>每条用例必须填写目标页面URL，平台会从该地址进入页面。</t>
-  </si>
-  <si>
-    <t>步骤拆分</t>
-  </si>
-  <si>
-    <t>操作过程写在步骤明细中，不要把多个动作写成一整段。</t>
-  </si>
-  <si>
-    <t>弹窗和跳转</t>
-  </si>
-  <si>
-    <t>如果点击后打开弹窗、跳转页面、打开新窗口，要写在操作描述中。</t>
-  </si>
-  <si>
-    <t>只写业务预期，例如页面提示保存成功、列表显示目标数据。</t>
-  </si>
-  <si>
-    <t>步骤明细中的数据引用必须和测试数据中的数据标识一致。</t>
-  </si>
-  <si>
-    <t>多个数据</t>
-  </si>
-  <si>
-    <t>同一步骤需要多个数据时，使用英文逗号分隔。</t>
+    <t>默认模板</t>
+  </si>
+  <si>
+    <t>新用户默认使用 用例清单 + 步骤明细 两张业务表，输入值和检查期望值直接填写。</t>
+  </si>
+  <si>
+    <t>用例清单</t>
+  </si>
+  <si>
+    <t>一行填写一条用例，目标页面URL必须填写，预期结果可填写最终业务现象。</t>
+  </si>
+  <si>
+    <t>步骤明细</t>
+  </si>
+  <si>
+    <t>一行填写一个操作或检查步骤，步骤序号从 1 开始连续递增。</t>
+  </si>
+  <si>
+    <t>使用中文下拉值，例如 点击(click)、填写(fill)、选择(select)、检查可见(assertVisible)。</t>
+  </si>
+  <si>
+    <t>使用中文下拉值，例如 按钮(button)、输入框(input)、文本(text)、表格(table)。</t>
+  </si>
+  <si>
+    <t>填写步骤填写输入值，检查步骤填写期望值。</t>
+  </si>
+  <si>
+    <t>检查类步骤可选择 包含(contains)、等于(equals)、正则(regex)。</t>
+  </si>
+  <si>
+    <t>新版两表模板</t>
+  </si>
+  <si>
+    <t>新版模板只维护用例清单和步骤明细，示例值直接写入输入/期望值。</t>
   </si>
 </sst>
 </file>
@@ -251,16 +223,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFD9E2F3"/>
+        <color rgb="FFD1D5DB"/>
       </left>
       <right style="thin">
-        <color rgb="FFD9E2F3"/>
+        <color rgb="FFD1D5DB"/>
       </right>
       <top style="thin">
-        <color rgb="FFD9E2F3"/>
+        <color rgb="FFD1D5DB"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFD9E2F3"/>
+        <color rgb="FFD1D5DB"/>
       </bottom>
       <diagonal/>
     </border>
@@ -283,10 +255,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -631,414 +609,391 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="22" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="22" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="34" customWidth="1"/>
-    <col min="5" max="5" width="42" customWidth="1"/>
-    <col min="6" max="6" width="28" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="36" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="26" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="4" t="s">
         <v>16</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultRowHeight="22" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <dimension ref="A1:T7"/>
+  <sheetFormatPr defaultRowHeight="22" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="34" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="6" max="6" width="28" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="26" customHeight="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="4">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="E2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="4">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="D3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="4">
         <v>3</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="4">
+        <v>4</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="4">
+        <v>1</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="E6" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2">
-        <v>4</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="G6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="2">
-        <v>1</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="2">
+      <c r="B7" s="4">
         <v>2</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="C7" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>23</v>
+      <c r="D7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:H1"/>
+  <dataValidations count="6">
+    <dataValidation type="list" showErrorMessage="1" errorTitle="动作类型不支持" error="请从下拉选项中选择动作类型" sqref="C10:C200">
+      <formula1>"打开页面(goto),点击(click),右键点击(rightClick),双击(doubleClick),悬停(hover),填写(fill),选择(select),等待(wait),检查文本(assertText),检查可见(assertVisible),检查输入值(assertValue),检查页面地址(assertUrl),检查页面标题(assertTitle)"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showErrorMessage="1" errorTitle="动作类型不支持" error="请从下拉选项中选择动作类型" sqref="C2:C200">
+      <formula1>"打开页面(goto),点击(click),右键点击(rightClick),双击(doubleClick),悬停(hover),填写(fill),选择(select),等待(wait),检查文本(assertText),检查可见(assertVisible),检查输入值(assertValue),检查页面地址(assertUrl),检查页面标题(assertTitle)"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showErrorMessage="1" errorTitle="目标类型不支持" error="请从下拉选项中选择目标类型" sqref="D10:D200">
+      <formula1>"页面(page),按钮(button),输入框(input),下拉框(select),链接(link),菜单(menu),页签(tab),弹窗(dialog),文本(text),表格(table),树(tree),日期控件(date),区域(region)"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showErrorMessage="1" errorTitle="目标类型不支持" error="请从下拉选项中选择目标类型" sqref="D2:D200">
+      <formula1>"页面(page),按钮(button),输入框(input),下拉框(select),链接(link),菜单(menu),页签(tab),弹窗(dialog),文本(text),表格(table),树(tree),日期控件(date),区域(region)"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="匹配方式不支持" error="请从下拉选项中选择匹配方式" sqref="G10:G200">
+      <formula1>"包含(contains),等于(equals),正则(regex)"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="匹配方式不支持" error="请从下拉选项中选择匹配方式" sqref="G2:G200">
+      <formula1>"包含(contains),等于(equals),正则(regex)"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="22" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="42" customWidth="1"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E1" s="1" t="s">
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="B1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="2" t="s">
+    </row>
+    <row r="2" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" s="2" t="s">
+    <row r="3" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E4" s="2" t="s">
+    </row>
+    <row r="5" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-  </sheetData>
-  <autoFilter ref="A1:E1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="22" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="76" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="6" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    </row>
+    <row r="7" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="2" t="s">
+    </row>
+    <row r="8" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="9" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:B1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/docs/ai-case-import/AI自然语言用例导入模板.xlsx
+++ b/docs/ai-case-import/AI自然语言用例导入模板.xlsx
@@ -688,7 +688,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T7"/>
+  <dimension ref="A1:H200"/>
   <sheetFormatPr defaultRowHeight="22" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -727,7 +727,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
@@ -753,7 +753,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -779,7 +779,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -805,7 +805,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -831,7 +831,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>12</v>
       </c>
@@ -857,7 +857,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>12</v>
       </c>
@@ -883,20 +883,213 @@
         <v>41</v>
       </c>
     </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25"/>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <dataValidations count="6">
     <dataValidation type="list" showErrorMessage="1" errorTitle="动作类型不支持" error="请从下拉选项中选择动作类型" sqref="C10:C200">
-      <formula1>"打开页面(goto),点击(click),右键点击(rightClick),双击(doubleClick),悬停(hover),填写(fill),选择(select),等待(wait),检查文本(assertText),检查可见(assertVisible),检查输入值(assertValue),检查页面地址(assertUrl),检查页面标题(assertTitle)"</formula1>
+      <formula1>"打开页面(goto),点击(click),右键点击(rightClick),双击(doubleClick),悬停(hover),填写(fill),选择(select),等待(wait),检查文本(assertText),检查可见(assertVisible),检查输入值(assertValue),检查地址(assertUrl),检查标题(assertTitle)"</formula1>
     </dataValidation>
     <dataValidation type="list" showErrorMessage="1" errorTitle="动作类型不支持" error="请从下拉选项中选择动作类型" sqref="C2:C200">
-      <formula1>"打开页面(goto),点击(click),右键点击(rightClick),双击(doubleClick),悬停(hover),填写(fill),选择(select),等待(wait),检查文本(assertText),检查可见(assertVisible),检查输入值(assertValue),检查页面地址(assertUrl),检查页面标题(assertTitle)"</formula1>
+      <formula1>"打开页面(goto),点击(click),右键点击(rightClick),双击(doubleClick),悬停(hover),填写(fill),选择(select),等待(wait),检查文本(assertText),检查可见(assertVisible),检查输入值(assertValue),检查地址(assertUrl),检查标题(assertTitle)"</formula1>
     </dataValidation>
     <dataValidation type="list" showErrorMessage="1" errorTitle="目标类型不支持" error="请从下拉选项中选择目标类型" sqref="D10:D200">
-      <formula1>"页面(page),按钮(button),输入框(input),下拉框(select),链接(link),菜单(menu),页签(tab),弹窗(dialog),文本(text),表格(table),树(tree),日期控件(date),区域(region)"</formula1>
+      <formula1>"页面(page),按钮(button),输入框(input),下拉框(select),链接(link),菜单(menu),页签(tab),弹窗(dialog),文本(text),表格(table),树节点(tree),日期控件(date),区域(region)"</formula1>
     </dataValidation>
     <dataValidation type="list" showErrorMessage="1" errorTitle="目标类型不支持" error="请从下拉选项中选择目标类型" sqref="D2:D200">
-      <formula1>"页面(page),按钮(button),输入框(input),下拉框(select),链接(link),菜单(menu),页签(tab),弹窗(dialog),文本(text),表格(table),树(tree),日期控件(date),区域(region)"</formula1>
+      <formula1>"页面(page),按钮(button),输入框(input),下拉框(select),链接(link),菜单(menu),页签(tab),弹窗(dialog),文本(text),表格(table),树节点(tree),日期控件(date),区域(region)"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="匹配方式不支持" error="请从下拉选项中选择匹配方式" sqref="G10:G200">
       <formula1>"包含(contains),等于(equals),正则(regex)"</formula1>

--- a/docs/ai-case-import/AI自然语言用例导入模板.xlsx
+++ b/docs/ai-case-import/AI自然语言用例导入模板.xlsx
@@ -1,19 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C23CEED2-1580-41FD-9EB6-E86980B9C564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="用例清单" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="步骤明细" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="填写说明" state="visible" r:id="rId6"/>
+    <sheet name="用例清单" sheetId="1" r:id="rId1"/>
+    <sheet name="步骤明细" sheetId="2" r:id="rId2"/>
+    <sheet name="填写说明" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="50">
   <si>
     <t>用例编号</t>
   </si>
@@ -36,168 +40,173 @@
     <t>TC001</t>
   </si>
   <si>
-    <t>新增用户</t>
-  </si>
-  <si>
-    <t>/user/list</t>
+    <t>步骤序号</t>
+  </si>
+  <si>
+    <t>动作类型</t>
+  </si>
+  <si>
+    <t>目标类型</t>
+  </si>
+  <si>
+    <t>目标名称</t>
+  </si>
+  <si>
+    <t>输入/期望值</t>
+  </si>
+  <si>
+    <t>匹配方式</t>
+  </si>
+  <si>
+    <t>点击(click)</t>
+  </si>
+  <si>
+    <t>按钮(button)</t>
+  </si>
+  <si>
+    <t>新增</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>填写(fill)</t>
+  </si>
+  <si>
+    <t>输入框(input)</t>
+  </si>
+  <si>
+    <t>选择(select)</t>
+  </si>
+  <si>
+    <t>下拉框(select)</t>
+  </si>
+  <si>
+    <t>项目</t>
+  </si>
+  <si>
+    <t>说明</t>
+  </si>
+  <si>
+    <t>默认模板</t>
+  </si>
+  <si>
+    <t>新用户默认使用 用例清单 + 步骤明细 两张业务表，输入值和检查期望值直接填写。</t>
+  </si>
+  <si>
+    <t>用例清单</t>
+  </si>
+  <si>
+    <t>一行填写一条用例，目标页面URL必须填写，预期结果可填写最终业务现象。</t>
+  </si>
+  <si>
+    <t>步骤明细</t>
+  </si>
+  <si>
+    <t>一行填写一个操作或检查步骤，步骤序号从 1 开始连续递增。</t>
+  </si>
+  <si>
+    <t>使用中文下拉值，例如 点击(click)、填写(fill)、选择(select)、检查可见(assertVisible)。</t>
+  </si>
+  <si>
+    <t>使用中文下拉值，例如 按钮(button)、输入框(input)、文本(text)、表格(table)。</t>
+  </si>
+  <si>
+    <t>填写步骤填写输入值，检查步骤填写期望值。</t>
+  </si>
+  <si>
+    <t>检查类步骤可选择 包含(contains)、等于(equals)、正则(regex)。</t>
+  </si>
+  <si>
+    <t>新版两表模板</t>
+  </si>
+  <si>
+    <t>新版模板只维护用例清单和步骤明细，示例值直接写入输入/期望值。</t>
+  </si>
+  <si>
+    <t>/web/IMQM07</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新增取样规则</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>已登录管理员账号，具备用户管理权限</t>
-  </si>
-  <si>
-    <t>页面提示保存成功，用户列表中显示新建用户</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>打开新增弹窗</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>页面表格第一条为新增的取样规则。取样名称为填写的取样名称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>取样名称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试取样名称001</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>取样简称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试取样简称001</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>取样类别</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>采购</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>人工</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>取样方式</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>目标页面URL为必填项</t>
   </si>
   <si>
-    <t>TC002</t>
-  </si>
-  <si>
-    <t>查询用户</t>
-  </si>
-  <si>
-    <t>已登录管理员账号，列表中已有测试用户001</t>
-  </si>
-  <si>
-    <t>用户列表只显示符合查询条件的用户</t>
-  </si>
-  <si>
     <t>查询条件直接填写在步骤明细的输入/期望值中</t>
-  </si>
-  <si>
-    <t>步骤序号</t>
-  </si>
-  <si>
-    <t>动作类型</t>
-  </si>
-  <si>
-    <t>目标类型</t>
-  </si>
-  <si>
-    <t>目标名称</t>
-  </si>
-  <si>
-    <t>输入/期望值</t>
-  </si>
-  <si>
-    <t>匹配方式</t>
-  </si>
-  <si>
-    <t>点击(click)</t>
-  </si>
-  <si>
-    <t>按钮(button)</t>
-  </si>
-  <si>
-    <t>新增</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>打开新增用户弹窗</t>
-  </si>
-  <si>
-    <t>填写(fill)</t>
-  </si>
-  <si>
-    <t>输入框(input)</t>
-  </si>
-  <si>
-    <t>用户名称</t>
-  </si>
-  <si>
-    <t>测试用户001</t>
-  </si>
-  <si>
-    <t>选择(select)</t>
-  </si>
-  <si>
-    <t>下拉框(select)</t>
-  </si>
-  <si>
-    <t>用户状态</t>
-  </si>
-  <si>
-    <t>启用</t>
-  </si>
-  <si>
-    <t>保存</t>
-  </si>
-  <si>
-    <t>用户名称查询条件</t>
-  </si>
-  <si>
-    <t>检查可见(assertVisible)</t>
-  </si>
-  <si>
-    <t>表格(table)</t>
-  </si>
-  <si>
-    <t>用户列表</t>
-  </si>
-  <si>
-    <t>检查查询结果可见</t>
-  </si>
-  <si>
-    <t>项目</t>
-  </si>
-  <si>
-    <t>说明</t>
-  </si>
-  <si>
-    <t>默认模板</t>
-  </si>
-  <si>
-    <t>新用户默认使用 用例清单 + 步骤明细 两张业务表，输入值和检查期望值直接填写。</t>
-  </si>
-  <si>
-    <t>用例清单</t>
-  </si>
-  <si>
-    <t>一行填写一条用例，目标页面URL必须填写，预期结果可填写最终业务现象。</t>
-  </si>
-  <si>
-    <t>步骤明细</t>
-  </si>
-  <si>
-    <t>一行填写一个操作或检查步骤，步骤序号从 1 开始连续递增。</t>
-  </si>
-  <si>
-    <t>使用中文下拉值，例如 点击(click)、填写(fill)、选择(select)、检查可见(assertVisible)。</t>
-  </si>
-  <si>
-    <t>使用中文下拉值，例如 按钮(button)、输入框(input)、文本(text)、表格(table)。</t>
-  </si>
-  <si>
-    <t>填写步骤填写输入值，检查步骤填写期望值。</t>
-  </si>
-  <si>
-    <t>检查类步骤可选择 包含(contains)、等于(equals)、正则(regex)。</t>
-  </si>
-  <si>
-    <t>新版两表模板</t>
-  </si>
-  <si>
-    <t>新版模板只维护用例清单和步骤明细，示例值直接写入输入/期望值。</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -255,7 +264,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -269,9 +278,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -607,9 +619,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="22" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="22" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -619,7 +631,7 @@
     <col min="6" max="6" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -639,57 +651,43 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" s="3" customFormat="1" ht="28" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>16</v>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F3" s="5" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H200"/>
-  <sheetFormatPr defaultRowHeight="22" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="22" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -701,33 +699,33 @@
     <col min="8" max="8" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" s="3" customFormat="1" ht="14" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
@@ -735,25 +733,25 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" s="3" customFormat="1" ht="14" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -761,25 +759,25 @@
         <v>2</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="3" customFormat="1" ht="14" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -787,25 +785,25 @@
         <v>3</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="14" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -813,300 +811,269 @@
         <v>4</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="14" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B6" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="4">
-        <v>2</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.25"/>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.25"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:8" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:8" ht="14" x14ac:dyDescent="0.25">
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:8" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:8" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:8" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:8" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:8" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:8" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:8" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="19" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="20" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="21" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="22" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="23" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="25" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="26" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="27" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="29" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="30" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="31" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="32" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="14" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="14" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
-  <dataValidations count="6">
-    <dataValidation type="list" showErrorMessage="1" errorTitle="动作类型不支持" error="请从下拉选项中选择动作类型" sqref="C10:C200">
+  <autoFilter ref="A1:H1" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <dataValidations count="3">
+    <dataValidation type="list" showErrorMessage="1" errorTitle="动作类型不支持" error="请从下拉选项中选择动作类型" sqref="C2:C198" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"打开页面(goto),点击(click),右键点击(rightClick),双击(doubleClick),悬停(hover),填写(fill),选择(select),等待(wait),检查文本(assertText),检查可见(assertVisible),检查输入值(assertValue),检查地址(assertUrl),检查标题(assertTitle)"</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" errorTitle="动作类型不支持" error="请从下拉选项中选择动作类型" sqref="C2:C200">
-      <formula1>"打开页面(goto),点击(click),右键点击(rightClick),双击(doubleClick),悬停(hover),填写(fill),选择(select),等待(wait),检查文本(assertText),检查可见(assertVisible),检查输入值(assertValue),检查地址(assertUrl),检查标题(assertTitle)"</formula1>
-    </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" errorTitle="目标类型不支持" error="请从下拉选项中选择目标类型" sqref="D10:D200">
+    <dataValidation type="list" showErrorMessage="1" errorTitle="目标类型不支持" error="请从下拉选项中选择目标类型" sqref="D2:D198" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"页面(page),按钮(button),输入框(input),下拉框(select),链接(link),菜单(menu),页签(tab),弹窗(dialog),文本(text),表格(table),树节点(tree),日期控件(date),区域(region)"</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" errorTitle="目标类型不支持" error="请从下拉选项中选择目标类型" sqref="D2:D200">
-      <formula1>"页面(page),按钮(button),输入框(input),下拉框(select),链接(link),菜单(menu),页签(tab),弹窗(dialog),文本(text),表格(table),树节点(tree),日期控件(date),区域(region)"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="匹配方式不支持" error="请从下拉选项中选择匹配方式" sqref="G10:G200">
-      <formula1>"包含(contains),等于(equals),正则(regex)"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="匹配方式不支持" error="请从下拉选项中选择匹配方式" sqref="G2:G200">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="匹配方式不支持" error="请从下拉选项中选择匹配方式" sqref="G2:G198" xr:uid="{00000000-0002-0000-0100-000004000000}">
       <formula1>"包含(contains),等于(equals),正则(regex)"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="80" customWidth="1"/>
@@ -1114,79 +1081,80 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="3" customFormat="1" ht="28" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1"/>
+  <autoFilter ref="A1:B1" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/docs/ai-case-import/AI自然语言用例导入模板.xlsx
+++ b/docs/ai-case-import/AI自然语言用例导入模板.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C23CEED2-1580-41FD-9EB6-E86980B9C564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC1CFE54-63EE-49BF-A53B-9CA2467A7F4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="49">
   <si>
     <t>用例编号</t>
   </si>
@@ -176,10 +176,8 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>目标页面URL为必填项</t>
-  </si>
-  <si>
-    <t>查询条件直接填写在步骤明细的输入/期望值中</t>
+    <t>目标页面URL为必填项。查询条件直接填写在步骤明细的输入/期望值中</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -651,7 +649,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="3" customFormat="1" ht="28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" s="3" customFormat="1" ht="42" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
@@ -672,9 +670,7 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F3" s="5" t="s">
-        <v>49</v>
-      </c>
+      <c r="F3" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
